--- a/data/raw/muqaththaah_dataset.xlsx
+++ b/data/raw/muqaththaah_dataset.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DataAnalyst\al-ahruf-al-muqaththaah-analysis\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889CDB81-887A-41F6-81FD-0D3EA21B5D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75097AC3-8466-4B77-B75A-CFA7EF09B5E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="15375" windowHeight="7875" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="15375" windowHeight="7875" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data_surah" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="88">
   <si>
     <t>kombinasi_huruf</t>
   </si>
@@ -229,9 +229,6 @@
   </si>
   <si>
     <t>al-Qur'an dan Tafsir, Vol.5 No.1, 2024, DOI: 10.59622/jiat.v5i1.114)</t>
-  </si>
-  <si>
-    <t>interpretasi_bisrimustofa</t>
   </si>
   <si>
     <t>Surah</t>
@@ -295,7 +292,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -330,13 +327,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -387,7 +377,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -399,18 +389,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -675,7 +661,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.5703125" customWidth="1"/>
@@ -686,829 +672,787 @@
     <col min="6" max="6" width="10.140625" customWidth="1"/>
     <col min="7" max="7" width="12.85546875" customWidth="1"/>
     <col min="8" max="8" width="23" customWidth="1"/>
-    <col min="9" max="9" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="C1" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="F1" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H1" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="G1" s="8" t="s">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="9">
+        <v>2</v>
+      </c>
+      <c r="C2" s="9">
+        <v>1</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="H1" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="F2" s="9">
+        <v>3</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="9">
+        <v>3</v>
+      </c>
+      <c r="C3" s="9">
+        <v>1</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3" s="9">
+        <v>3</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="9">
+        <v>7</v>
+      </c>
+      <c r="C4" s="9">
+        <v>1</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="F4" s="9">
+        <v>4</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="9">
+        <v>10</v>
+      </c>
+      <c r="C5" s="9">
+        <v>1</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F5" s="9">
+        <v>3</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="9">
+        <v>11</v>
+      </c>
+      <c r="C6" s="9">
+        <v>1</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F6" s="9">
+        <v>3</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="9">
+        <v>12</v>
+      </c>
+      <c r="C7" s="9">
+        <v>1</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F7" s="9">
+        <v>3</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="9">
+        <v>13</v>
+      </c>
+      <c r="C8" s="9">
+        <v>1</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" s="9">
+        <v>4</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="9">
+        <v>14</v>
+      </c>
+      <c r="C9" s="9">
+        <v>1</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F9" s="9">
+        <v>3</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="9">
+        <v>15</v>
+      </c>
+      <c r="C10" s="9">
+        <v>1</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F10" s="9">
+        <v>3</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="9">
+        <v>19</v>
+      </c>
+      <c r="C11" s="9">
+        <v>1</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" s="9">
+        <v>5</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="9">
+        <v>20</v>
+      </c>
+      <c r="C12" s="9">
+        <v>1</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" s="9">
         <v>2</v>
       </c>
-      <c r="B2" s="10">
+      <c r="G12" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="9">
+        <v>26</v>
+      </c>
+      <c r="C13" s="9">
+        <v>1</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F13" s="9">
+        <v>3</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="9">
+        <v>27</v>
+      </c>
+      <c r="C14" s="9">
+        <v>1</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F14" s="9">
         <v>2</v>
       </c>
-      <c r="C2" s="10">
-        <v>1</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="F2" s="10">
-        <v>3</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="H2" s="11" t="s">
+      <c r="G14" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="9">
+        <v>28</v>
+      </c>
+      <c r="C15" s="9">
+        <v>1</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F15" s="9">
+        <v>3</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="9">
+        <v>29</v>
+      </c>
+      <c r="C16" s="9">
+        <v>1</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F16" s="9">
+        <v>3</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="9">
+        <v>30</v>
+      </c>
+      <c r="C17" s="9">
+        <v>1</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F17" s="9">
+        <v>3</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="9">
+        <v>31</v>
+      </c>
+      <c r="C18" s="9">
+        <v>1</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F18" s="9">
+        <v>3</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="9">
+        <v>32</v>
+      </c>
+      <c r="C19" s="9">
+        <v>1</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F19" s="9">
+        <v>3</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="9">
+        <v>36</v>
+      </c>
+      <c r="C20" s="9">
+        <v>1</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F20" s="9">
+        <v>2</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H20" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="I2" s="12"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="10">
-        <v>3</v>
-      </c>
-      <c r="C3" s="10">
-        <v>1</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="F3" s="10">
-        <v>3</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="I3" s="12"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="9">
+        <v>38</v>
+      </c>
+      <c r="C21" s="9">
+        <v>1</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="F21" s="9">
+        <v>1</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="9">
+        <v>40</v>
+      </c>
+      <c r="C22" s="9">
+        <v>1</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F22" s="9">
+        <v>2</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="9">
+        <v>41</v>
+      </c>
+      <c r="C23" s="9">
+        <v>1</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F23" s="9">
+        <v>2</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="9">
+        <v>42</v>
+      </c>
+      <c r="C24" s="9">
+        <v>1</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F24" s="9">
         <v>5</v>
       </c>
-      <c r="B4" s="10">
-        <v>7</v>
-      </c>
-      <c r="C4" s="10">
-        <v>1</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="F4" s="10">
-        <v>4</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="I4" s="12"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="10">
-        <v>10</v>
-      </c>
-      <c r="C5" s="10">
-        <v>1</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="F5" s="10">
-        <v>3</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="I5" s="12"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="10">
-        <v>11</v>
-      </c>
-      <c r="C6" s="10">
-        <v>1</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="F6" s="10">
-        <v>3</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="I6" s="12"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="10">
-        <v>12</v>
-      </c>
-      <c r="C7" s="10">
-        <v>1</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="F7" s="10">
-        <v>3</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="I7" s="12"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="10">
-        <v>13</v>
-      </c>
-      <c r="C8" s="10">
-        <v>1</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="F8" s="10">
-        <v>4</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="I8" s="12"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="10">
-        <v>14</v>
-      </c>
-      <c r="C9" s="10">
-        <v>1</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="F9" s="10">
-        <v>3</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="I9" s="12"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="10">
-        <v>15</v>
-      </c>
-      <c r="C10" s="10">
-        <v>1</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="F10" s="10">
-        <v>3</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="I10" s="12"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="10">
-        <v>19</v>
-      </c>
-      <c r="C11" s="10">
-        <v>1</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="11" t="s">
+      <c r="G24" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="9">
+        <v>43</v>
+      </c>
+      <c r="C25" s="9">
+        <v>1</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E25" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="F11" s="10">
-        <v>5</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="I11" s="12"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="10">
-        <v>20</v>
-      </c>
-      <c r="C12" s="10">
-        <v>1</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="F12" s="10">
+      <c r="F25" s="9">
         <v>2</v>
       </c>
-      <c r="G12" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="I12" s="12"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="10">
-        <v>26</v>
-      </c>
-      <c r="C13" s="10">
-        <v>1</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="F13" s="10">
-        <v>3</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="I13" s="12"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="10">
-        <v>27</v>
-      </c>
-      <c r="C14" s="10">
-        <v>1</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="F14" s="10">
+      <c r="G25" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="9">
+        <v>44</v>
+      </c>
+      <c r="C26" s="9">
+        <v>1</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F26" s="9">
         <v>2</v>
       </c>
-      <c r="G14" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="I14" s="12"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="10">
-        <v>28</v>
-      </c>
-      <c r="C15" s="10">
-        <v>1</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="F15" s="10">
-        <v>3</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="I15" s="12"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="10">
-        <v>29</v>
-      </c>
-      <c r="C16" s="10">
-        <v>1</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="F16" s="10">
-        <v>3</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H16" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="I16" s="12"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="10">
-        <v>30</v>
-      </c>
-      <c r="C17" s="10">
-        <v>1</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="F17" s="10">
-        <v>3</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="I17" s="12"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="10">
-        <v>31</v>
-      </c>
-      <c r="C18" s="10">
-        <v>1</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="F18" s="10">
-        <v>3</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="I18" s="12"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="10">
-        <v>32</v>
-      </c>
-      <c r="C19" s="10">
-        <v>1</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="F19" s="10">
-        <v>3</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="I19" s="12"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" s="10">
-        <v>36</v>
-      </c>
-      <c r="C20" s="10">
-        <v>1</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="F20" s="10">
+      <c r="G26" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="9">
+        <v>45</v>
+      </c>
+      <c r="C27" s="9">
+        <v>1</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F27" s="9">
         <v>2</v>
       </c>
-      <c r="G20" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H20" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="I20" s="12"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B21" s="10">
-        <v>38</v>
-      </c>
-      <c r="C21" s="10">
-        <v>1</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" s="11" t="s">
+      <c r="G27" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="9">
+        <v>46</v>
+      </c>
+      <c r="C28" s="9">
+        <v>1</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F28" s="9">
+        <v>2</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="9">
+        <v>50</v>
+      </c>
+      <c r="C29" s="9">
+        <v>1</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E29" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="F21" s="10">
-        <v>1</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="I21" s="12"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" s="10">
-        <v>40</v>
-      </c>
-      <c r="C22" s="10">
-        <v>1</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="F22" s="10">
-        <v>2</v>
-      </c>
-      <c r="G22" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H22" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="I22" s="12"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B23" s="10">
-        <v>41</v>
-      </c>
-      <c r="C23" s="10">
-        <v>1</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="F23" s="10">
-        <v>2</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="I23" s="12"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" s="10">
-        <v>42</v>
-      </c>
-      <c r="C24" s="10">
-        <v>1</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="F24" s="10">
-        <v>5</v>
-      </c>
-      <c r="G24" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H24" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="I24" s="12"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="10">
+      <c r="F29" s="9">
+        <v>1</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C25" s="10">
-        <v>1</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="F25" s="10">
-        <v>2</v>
-      </c>
-      <c r="G25" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="I25" s="12"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="10">
+      <c r="B30" s="9">
+        <v>68</v>
+      </c>
+      <c r="C30" s="9">
+        <v>1</v>
+      </c>
+      <c r="D30" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C26" s="10">
-        <v>1</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="F26" s="10">
-        <v>2</v>
-      </c>
-      <c r="G26" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H26" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="I26" s="12"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="10">
-        <v>45</v>
-      </c>
-      <c r="C27" s="10">
-        <v>1</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="F27" s="10">
-        <v>2</v>
-      </c>
-      <c r="G27" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="I27" s="12"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="10">
-        <v>46</v>
-      </c>
-      <c r="C28" s="10">
-        <v>1</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="F28" s="10">
-        <v>2</v>
-      </c>
-      <c r="G28" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H28" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="I28" s="12"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="10">
-        <v>50</v>
-      </c>
-      <c r="C29" s="10">
-        <v>1</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="F29" s="10">
-        <v>1</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="I29" s="12"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30" s="10">
-        <v>68</v>
-      </c>
-      <c r="C30" s="10">
-        <v>1</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="F30" s="10">
-        <v>1</v>
-      </c>
-      <c r="G30" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H30" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="I30" s="12"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C31" s="2"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C32" s="2"/>
-    </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C33" s="2"/>
+      <c r="E30" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="F30" s="9">
+        <v>1</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>82</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/raw/muqaththaah_dataset.xlsx
+++ b/data/raw/muqaththaah_dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DataAnalyst\al-ahruf-al-muqaththaah-analysis\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75097AC3-8466-4B77-B75A-CFA7EF09B5E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4DC295E-B5D8-4F45-A65B-DFCA70AE5825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1950" windowWidth="15375" windowHeight="7875" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -231,9 +231,6 @@
     <t>al-Qur'an dan Tafsir, Vol.5 No.1, 2024, DOI: 10.59622/jiat.v5i1.114)</t>
   </si>
   <si>
-    <t>Surah</t>
-  </si>
-  <si>
     <t>Surah_Number</t>
   </si>
   <si>
@@ -286,6 +283,9 @@
   </si>
   <si>
     <t>Muqaththaah</t>
+  </si>
+  <si>
+    <t>Surah_Name</t>
   </si>
 </sst>
 </file>
@@ -664,7 +664,7 @@
   <dimension ref="A1:H30"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
@@ -676,28 +676,28 @@
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="F1" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="7" t="s">
         <v>80</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -714,16 +714,16 @@
         <v>3</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F2" s="9">
         <v>3</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -740,16 +740,16 @@
         <v>3</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F3" s="9">
         <v>3</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -766,16 +766,16 @@
         <v>6</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F4" s="9">
         <v>4</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -792,16 +792,16 @@
         <v>8</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F5" s="9">
         <v>3</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -818,16 +818,16 @@
         <v>8</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F6" s="9">
         <v>3</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -844,16 +844,16 @@
         <v>8</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F7" s="9">
         <v>3</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -870,16 +870,16 @@
         <v>12</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F8" s="9">
         <v>4</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -896,16 +896,16 @@
         <v>8</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F9" s="9">
         <v>3</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -922,16 +922,16 @@
         <v>8</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F10" s="9">
         <v>3</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -948,16 +948,16 @@
         <v>16</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F11" s="9">
         <v>5</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -974,16 +974,16 @@
         <v>18</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F12" s="9">
         <v>2</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -1000,16 +1000,16 @@
         <v>20</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F13" s="9">
         <v>3</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -1026,16 +1026,16 @@
         <v>22</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F14" s="9">
         <v>2</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -1052,16 +1052,16 @@
         <v>20</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F15" s="9">
         <v>3</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1078,16 +1078,16 @@
         <v>3</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F16" s="9">
         <v>3</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1104,16 +1104,16 @@
         <v>3</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F17" s="9">
         <v>3</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1130,16 +1130,16 @@
         <v>3</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F18" s="9">
         <v>3</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1156,16 +1156,16 @@
         <v>3</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F19" s="9">
         <v>3</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1182,16 +1182,16 @@
         <v>29</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F20" s="9">
         <v>2</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1208,16 +1208,16 @@
         <v>31</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F21" s="9">
         <v>1</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1234,16 +1234,16 @@
         <v>33</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F22" s="9">
         <v>2</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1260,16 +1260,16 @@
         <v>33</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F23" s="9">
         <v>2</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1286,16 +1286,16 @@
         <v>36</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F24" s="9">
         <v>5</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1312,16 +1312,16 @@
         <v>33</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F25" s="9">
         <v>2</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1338,16 +1338,16 @@
         <v>33</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F26" s="9">
         <v>2</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1364,16 +1364,16 @@
         <v>33</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F27" s="9">
         <v>2</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1390,16 +1390,16 @@
         <v>33</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F28" s="9">
         <v>2</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1416,16 +1416,16 @@
         <v>42</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F29" s="9">
         <v>1</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1442,16 +1442,16 @@
         <v>44</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F30" s="9">
         <v>1</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
